--- a/data/trans_dic/P55$familiar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 34,4</t>
+          <t>7,9; 35,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 46,7</t>
+          <t>12,49; 42,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,11; 57,74</t>
+          <t>24,01; 56,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,06; 66,78</t>
+          <t>45,18; 65,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,93; 39,99</t>
+          <t>13,65; 40,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,01; 50,49</t>
+          <t>24,03; 49,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,67; 41,66</t>
+          <t>17,39; 41,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,41; 68,46</t>
+          <t>53,6; 67,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 33,54</t>
+          <t>13,34; 33,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,87; 42,54</t>
+          <t>23,98; 43,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,03; 42,2</t>
+          <t>22,83; 42,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,1; 65,22</t>
+          <t>53,06; 65,11</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 28,6</t>
+          <t>8,24; 30,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 41,94</t>
+          <t>16,61; 44,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 49,04</t>
+          <t>21,03; 47,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,36; 68,62</t>
+          <t>44,34; 67,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 45,21</t>
+          <t>21,66; 45,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,43; 44,0</t>
+          <t>22,81; 43,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 38,56</t>
+          <t>16,78; 39,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,95; 70,45</t>
+          <t>56,6; 70,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 35,2</t>
+          <t>17,85; 34,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 38,87</t>
+          <t>22,54; 39,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 38,71</t>
+          <t>21,39; 39,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 67,13</t>
+          <t>54,89; 67,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 52,85</t>
+          <t>11,61; 52,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 39,24</t>
+          <t>7,01; 37,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 42,02</t>
+          <t>8,41; 45,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,61; 60,92</t>
+          <t>25,79; 60,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 46,22</t>
+          <t>15,77; 42,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 41,65</t>
+          <t>15,72; 40,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 41,27</t>
+          <t>14,53; 42,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,05; 67,2</t>
+          <t>47,49; 66,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 40,28</t>
+          <t>18,32; 40,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,42; 34,86</t>
+          <t>15,24; 34,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 35,66</t>
+          <t>15,0; 36,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,05; 61,38</t>
+          <t>44,41; 61,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 37,17</t>
+          <t>6,93; 37,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 35,56</t>
+          <t>9,56; 35,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 34,71</t>
+          <t>7,79; 34,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 60,53</t>
+          <t>35,45; 59,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 25,41</t>
+          <t>7,64; 26,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 41,76</t>
+          <t>21,32; 42,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 42,86</t>
+          <t>19,36; 41,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 59,62</t>
+          <t>45,59; 60,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 26,25</t>
+          <t>9,61; 25,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 36,44</t>
+          <t>19,33; 36,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 37,23</t>
+          <t>18,85; 37,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,42; 57,44</t>
+          <t>44,99; 57,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,41</t>
+          <t>13,87; 28,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,96</t>
+          <t>16,53; 31,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,51; 37,22</t>
+          <t>21,89; 36,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,24; 57,42</t>
+          <t>44,77; 57,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 31,66</t>
+          <t>19,92; 31,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,68; 37,75</t>
+          <t>26,5; 37,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,57</t>
+          <t>22,36; 34,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>55,09; 62,54</t>
+          <t>54,41; 62,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,96</t>
+          <t>19,05; 28,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,36; 33,38</t>
+          <t>24,47; 33,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,68</t>
+          <t>23,37; 33,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,86; 59,54</t>
+          <t>52,79; 59,39</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2788; 11652</t>
+          <t>2675; 12038</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3962; 15195</t>
+          <t>4063; 13959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6697; 16038</t>
+          <t>6669; 15824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22361; 33139</t>
+          <t>22422; 32667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6240; 17910</t>
+          <t>6113; 18096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15256; 30802</t>
+          <t>14658; 30117</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10627; 25056</t>
+          <t>10457; 25013</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43353; 54545</t>
+          <t>42701; 54063</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11291; 26381</t>
+          <t>10495; 25990</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21391; 39796</t>
+          <t>22432; 40312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20243; 37102</t>
+          <t>20071; 37220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68663; 84322</t>
+          <t>68604; 84192</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3747; 13733</t>
+          <t>3955; 14463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6729; 19148</t>
+          <t>7582; 20331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8607; 20062</t>
+          <t>8605; 19416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16777; 26551</t>
+          <t>17154; 26162</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15004; 30596</t>
+          <t>14662; 31129</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18927; 38870</t>
+          <t>20151; 38666</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12687; 29632</t>
+          <t>12893; 30635</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48116; 60583</t>
+          <t>48678; 60786</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21167; 40722</t>
+          <t>20648; 39726</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30156; 52089</t>
+          <t>30203; 52629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24919; 45581</t>
+          <t>25190; 46452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68786; 83707</t>
+          <t>68437; 84392</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2591; 11403</t>
+          <t>2504; 11299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1895; 10964</t>
+          <t>1959; 10499</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1778; 9776</t>
+          <t>1957; 10596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6794; 15552</t>
+          <t>6584; 15447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8407; 21475</t>
+          <t>7329; 19964</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8527; 21624</t>
+          <t>8159; 21272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7806; 21285</t>
+          <t>7492; 21696</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28016; 39187</t>
+          <t>27694; 38727</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12648; 27403</t>
+          <t>12465; 27386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12314; 27840</t>
+          <t>12167; 27841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11351; 26683</t>
+          <t>11226; 26996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36931; 51456</t>
+          <t>37234; 51497</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1604; 8589</t>
+          <t>1602; 8598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3957; 14237</t>
+          <t>3826; 14128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2356; 10243</t>
+          <t>2299; 10094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15700; 26165</t>
+          <t>15323; 25626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5703; 18296</t>
+          <t>5502; 19033</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15739; 32691</t>
+          <t>16690; 33581</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15030; 33782</t>
+          <t>15258; 32795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47497; 62163</t>
+          <t>47534; 62601</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10086; 24960</t>
+          <t>9141; 24100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23651; 43114</t>
+          <t>22866; 42685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19396; 40326</t>
+          <t>20422; 41056</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66991; 84723</t>
+          <t>66361; 84349</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16410; 33428</t>
+          <t>17560; 35546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24227; 45248</t>
+          <t>24159; 46071</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26123; 45209</t>
+          <t>26582; 44854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71058; 90192</t>
+          <t>70318; 89567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45180; 73115</t>
+          <t>45999; 73873</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74576; 105523</t>
+          <t>74063; 105453</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58493; 92435</t>
+          <t>59795; 92871</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>180821; 205271</t>
+          <t>178607; 204104</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67956; 99972</t>
+          <t>68120; 100743</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103687; 142104</t>
+          <t>104150; 142057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93890; 130956</t>
+          <t>90859; 129260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>256524; 288971</t>
+          <t>256200; 288244</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 35,54</t>
+          <t>8,05; 36,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 42,9</t>
+          <t>12,32; 44,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 56,97</t>
+          <t>24,44; 58,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,18; 65,83</t>
+          <t>44,42; 65,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,65; 40,41</t>
+          <t>13,99; 40,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,03; 49,37</t>
+          <t>25,64; 51,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 41,59</t>
+          <t>17,19; 42,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,6; 67,86</t>
+          <t>53,77; 68,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 33,04</t>
+          <t>14,46; 33,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,98; 43,1</t>
+          <t>23,02; 43,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 42,34</t>
+          <t>23,21; 42,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,06; 65,11</t>
+          <t>52,42; 65,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 30,12</t>
+          <t>7,94; 28,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 44,53</t>
+          <t>14,38; 42,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 47,46</t>
+          <t>20,18; 47,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,34; 67,62</t>
+          <t>42,32; 66,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 45,99</t>
+          <t>22,97; 45,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,81; 43,77</t>
+          <t>22,5; 42,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 39,87</t>
+          <t>16,3; 39,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,6; 70,68</t>
+          <t>53,47; 68,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 34,33</t>
+          <t>18,03; 34,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,54; 39,28</t>
+          <t>22,44; 39,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,39; 39,45</t>
+          <t>21,69; 40,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,89; 67,68</t>
+          <t>53,52; 66,22</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 52,37</t>
+          <t>11,23; 52,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 37,58</t>
+          <t>6,61; 38,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 45,55</t>
+          <t>7,65; 40,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,79; 60,51</t>
+          <t>22,87; 55,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,77; 42,97</t>
+          <t>16,89; 43,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 40,97</t>
+          <t>16,16; 40,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 42,07</t>
+          <t>12,99; 40,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,49; 66,42</t>
+          <t>45,88; 64,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 40,25</t>
+          <t>18,63; 43,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,24; 34,86</t>
+          <t>15,54; 34,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 36,07</t>
+          <t>14,56; 37,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,41; 61,42</t>
+          <t>41,99; 58,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 37,21</t>
+          <t>7,0; 35,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 35,29</t>
+          <t>9,51; 35,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 34,21</t>
+          <t>7,57; 34,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 59,28</t>
+          <t>35,6; 57,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 26,44</t>
+          <t>8,07; 27,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 42,9</t>
+          <t>21,69; 42,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,36; 41,61</t>
+          <t>19,4; 43,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,59; 60,04</t>
+          <t>44,73; 59,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 25,34</t>
+          <t>9,83; 25,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 36,08</t>
+          <t>20,08; 36,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 37,9</t>
+          <t>17,47; 36,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,99; 57,19</t>
+          <t>43,82; 56,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,08</t>
+          <t>13,68; 27,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,52</t>
+          <t>16,22; 31,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,93</t>
+          <t>21,9; 36,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,77; 57,02</t>
+          <t>43,59; 55,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,99</t>
+          <t>19,9; 31,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,5; 37,72</t>
+          <t>26,4; 37,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,36; 34,74</t>
+          <t>22,32; 34,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,41; 62,18</t>
+          <t>53,59; 61,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,18</t>
+          <t>19,27; 28,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 33,37</t>
+          <t>24,25; 33,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,24</t>
+          <t>23,35; 33,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,39</t>
+          <t>51,54; 58,16</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48917</t>
+          <t>51680</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76481</t>
+          <t>80783</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2675; 12038</t>
+          <t>2729; 12265</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4063; 13959</t>
+          <t>4010; 14379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6669; 15824</t>
+          <t>6788; 16168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22422; 32667</t>
+          <t>23542; 34839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6113; 18096</t>
+          <t>6267; 18115</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14658; 30117</t>
+          <t>15638; 31326</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10457; 25013</t>
+          <t>10336; 25692</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42701; 54063</t>
+          <t>45635; 58447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10495; 25990</t>
+          <t>11375; 26299</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22432; 40312</t>
+          <t>21536; 40637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20071; 37220</t>
+          <t>20405; 37521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68604; 84192</t>
+          <t>72268; 89774</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>58661</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>81676</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3955; 14463</t>
+          <t>3811; 13728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7582; 20331</t>
+          <t>6567; 19379</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8605; 19416</t>
+          <t>8256; 19237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17154; 26162</t>
+          <t>17714; 27818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14662; 31129</t>
+          <t>15549; 30515</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20151; 38666</t>
+          <t>19875; 37540</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12893; 30635</t>
+          <t>12524; 30680</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48678; 60786</t>
+          <t>50605; 65182</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20648; 39726</t>
+          <t>20865; 39571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30203; 52629</t>
+          <t>30065; 52517</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25190; 46452</t>
+          <t>25544; 47190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68437; 84392</t>
+          <t>73050; 90390</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33426</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43985</t>
+          <t>47818</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2504; 11299</t>
+          <t>2422; 11258</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1959; 10499</t>
+          <t>1846; 10648</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1957; 10596</t>
+          <t>1779; 9474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6584; 15447</t>
+          <t>6795; 16420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7329; 19964</t>
+          <t>7848; 20186</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8159; 21272</t>
+          <t>8389; 21003</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7492; 21696</t>
+          <t>6698; 20856</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27694; 38727</t>
+          <t>29777; 41944</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12465; 27386</t>
+          <t>12678; 29528</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12167; 27841</t>
+          <t>12411; 27835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11226; 26996</t>
+          <t>10896; 27945</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37234; 51497</t>
+          <t>39722; 55131</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55218</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>79716</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1602; 8598</t>
+          <t>1617; 8316</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3826; 14128</t>
+          <t>3806; 14200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2299; 10094</t>
+          <t>2235; 10061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15323; 25626</t>
+          <t>15865; 25765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5502; 19033</t>
+          <t>5812; 19806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16690; 33581</t>
+          <t>16981; 33220</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15258; 32795</t>
+          <t>15290; 34533</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47534; 62601</t>
+          <t>50475; 67643</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9141; 24100</t>
+          <t>9347; 24100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22866; 42685</t>
+          <t>23753; 43421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20422; 41056</t>
+          <t>18927; 39151</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66361; 84349</t>
+          <t>68977; 88784</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>192209</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>272302</t>
+          <t>289993</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17560; 35546</t>
+          <t>17321; 35325</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24159; 46071</t>
+          <t>23707; 45501</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26582; 44854</t>
+          <t>26604; 44783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70318; 89567</t>
+          <t>73721; 94448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45999; 73873</t>
+          <t>45953; 73648</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74063; 105453</t>
+          <t>73799; 105405</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59795; 92871</t>
+          <t>59683; 92419</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>178607; 204104</t>
+          <t>191431; 218341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68120; 100743</t>
+          <t>68901; 101870</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104150; 142057</t>
+          <t>103211; 142669</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90859; 129260</t>
+          <t>90803; 128435</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>256200; 288244</t>
+          <t>271305; 306124</t>
         </is>
       </c>
     </row>
